--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -50,7 +50,7 @@
     <t>ng-observation</t>
   </si>
   <si>
-    <t>Nigeria Core Composite Observation</t>
+    <t>NG Composite Observation</t>
   </si>
   <si>
     <t>Observation Category Codes#social-history</t>
@@ -95,7 +95,7 @@
     <t>ng-observation-alcohol-use</t>
   </si>
   <si>
-    <t>Nigeria Core Alcohol Use Observation</t>
+    <t>NG Alcohol Use Observation</t>
   </si>
   <si>
     <t>LOINC#74013-4</t>
@@ -104,7 +104,7 @@
     <t>ng-observation-pregnancy-edd</t>
   </si>
   <si>
-    <t>Nigeria Core Pregnancy Expected Delivery Date Observation</t>
+    <t>NG Pregnancy EDD Observation</t>
   </si>
   <si>
     <t>LOINC#11778-8</t>
@@ -113,7 +113,7 @@
     <t>ng-observation-pregnancy-outcome</t>
   </si>
   <si>
-    <t>Nigeria Core Pregnancy Outcome Observation</t>
+    <t>NG Pregnancy Outcome Observation</t>
   </si>
   <si>
     <t>LOINC#64710-7</t>
@@ -122,13 +122,13 @@
     <t>ng-observation-pregnancy-status</t>
   </si>
   <si>
-    <t>Nigeria Core Pregnancy Status Observation</t>
+    <t>NG Pregnancy Status Observation</t>
   </si>
   <si>
     <t>ng-observation-results-laboratory-pathology</t>
   </si>
   <si>
-    <t>Nigeria Core Laboratory or Pathology Result Observation</t>
+    <t>NG Laboratory or Pathology Result Observation</t>
   </si>
   <si>
     <t>Observation Category Codes#laboratory</t>
@@ -146,7 +146,7 @@
     <t>ng-observation-results-radiology</t>
   </si>
   <si>
-    <t>Nigeria Core Radiology Result Observation</t>
+    <t>NG Radiology Result Observation</t>
   </si>
   <si>
     <t>Observation Category Codes#imaging</t>
@@ -161,7 +161,7 @@
     <t>ng-observation-tobacco-use</t>
   </si>
   <si>
-    <t>Nigeria Core Tobacco Smoking Status Observation</t>
+    <t>NG Tobacco Smoking Status Observation</t>
   </si>
   <si>
     <t>LOINC#72166-2</t>
